--- a/visualization/1_individual_stats.xlsx
+++ b/visualization/1_individual_stats.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <workbookPr codeName="Ten_skoroszyt"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateusz\Desktop\ZBIORCZE\TECH\ANALIZA DANYCH\SQL\VS\Projekty MB\SQL Analysis of International Football Results\visualization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mateusz\Desktop\ZBIORCZE\TECH\ANALIZA DANYCH\SQL\Projekty MB\SQL-Analysis-of-International-Football-Results\visualization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ACB398C-79C1-4507-9CD4-921CEC211BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B10CC5D-4F08-4B12-918D-8A5E30325953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection lockStructure="1"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -1740,41 +1740,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="27442">
-              <a:srgbClr val="DEEBF7"/>
-            </a:gs>
-            <a:gs pos="26492">
-              <a:srgbClr val="DFECF7"/>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -2782,35 +2750,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -2955,7 +2897,9 @@
       </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:noFill/>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -3021,7 +2965,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F4998CA9-9935-4CF8-B9C1-A2297CEDA28B}" type="CELLRANGE">
+                    <a:fld id="{0433C06D-E80A-4A3D-8BBF-EFD0F806C497}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3054,7 +2998,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{59643573-89CA-4396-AC3F-0A789E02D66A}" type="CELLRANGE">
+                    <a:fld id="{5FE2D854-75E0-4CBB-AB57-431B1767EBA6}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3088,7 +3032,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{74D8E9D6-7693-4E27-993F-1DA0997DE3BA}" type="CELLRANGE">
+                    <a:fld id="{B1829648-2325-4733-A705-38E971A92E17}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3122,7 +3066,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{128BFCDD-2DD6-4F2A-B2FE-D6EF1085AD56}" type="CELLRANGE">
+                    <a:fld id="{330B5DE6-7862-4F9B-8299-3D76051DBCDE}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3156,7 +3100,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FE6BE713-8F50-424D-95DC-FE0D3FB358E7}" type="CELLRANGE">
+                    <a:fld id="{571FA99D-B944-45C3-B086-1FED0157F87D}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3190,7 +3134,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A1731ADA-F5D9-45DA-9A91-8F95B5FC8A6F}" type="CELLRANGE">
+                    <a:fld id="{5AFC4CCB-6745-4D29-8CA2-4417B7CBB240}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3224,7 +3168,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{46F33533-29FD-4383-9CFB-4A7C0D2F9445}" type="CELLRANGE">
+                    <a:fld id="{D232ED22-F993-4C70-98DF-8F503493143B}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3258,7 +3202,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E3E711FA-8423-4522-92D7-E2FE4C0D9D6B}" type="CELLRANGE">
+                    <a:fld id="{7954DA64-B6FC-49FA-BDE4-176808D39536}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3292,7 +3236,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{9187D49C-605A-454E-A115-FE5B346A692A}" type="CELLRANGE">
+                    <a:fld id="{663126D6-C6E1-450D-9389-2A7416EBB211}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3326,7 +3270,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{FEC9307E-D42E-4136-8E69-47D191A4F087}" type="CELLRANGE">
+                    <a:fld id="{AAECF91C-44D6-4C83-A756-2A83EC5CAFDC}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3360,7 +3304,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{82FEC92F-645B-4E47-93DE-20B03928E7DB}" type="CELLRANGE">
+                    <a:fld id="{8EC2A012-CAE8-40A8-B25F-BA7CE2855294}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3394,7 +3338,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5D2B9B63-9AAC-469B-9BED-C87E22043398}" type="CELLRANGE">
+                    <a:fld id="{96A6B6F7-B16D-4BD0-A1BA-D3BB1C3838D0}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3428,7 +3372,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{60D18D21-A239-483B-B7A4-6ED59CF6C1E9}" type="CELLRANGE">
+                    <a:fld id="{7B6A1AD2-3BEB-49A9-8E9E-B35CD991BC93}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3462,7 +3406,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D93EBF45-5222-4E47-8BDF-296ECAC2960A}" type="CELLRANGE">
+                    <a:fld id="{057E4D66-9EEF-4418-817C-C86B9D0A395A}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3496,7 +3440,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C63A82E9-1706-411A-88F2-D67CBB232D64}" type="CELLRANGE">
+                    <a:fld id="{9D7C440F-490E-45CA-8A30-36A79A26DC71}" type="CELLRANGE">
                       <a:rPr lang="pl-PL"/>
                       <a:pPr/>
                       <a:t>[ZAKRES KOMÓREK]</a:t>
@@ -3990,35 +3934,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4786,35 +4704,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -5461,35 +5353,9 @@
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="5000"/>
-                <a:lumOff val="95000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="74000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="83000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="45000"/>
-                <a:lumOff val="55000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="accent1">
-                <a:lumMod val="30000"/>
-                <a:lumOff val="70000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:sysClr val="window" lastClr="FFFFFF"/>
+        </a:solidFill>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -8797,7 +8663,7 @@
 
 <file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{DE000BBD-59D5-44B0-9E5A-2A6C1680F05F}">
-  <sheetPr/>
+  <sheetPr codeName="Wykres1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8805,7 +8671,7 @@
 
 <file path=xl/chartsheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{50FB2B61-EAAA-46D4-BB62-2C9F4639852B}">
-  <sheetPr/>
+  <sheetPr codeName="Wykres3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8813,7 +8679,7 @@
 
 <file path=xl/chartsheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{6B6E693D-F51A-4F94-8590-D2EDC1D02BB1}">
-  <sheetPr/>
+  <sheetPr codeName="Wykres5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8821,7 +8687,7 @@
 
 <file path=xl/chartsheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{D5EC61BE-A9C8-4971-BD80-A7A22E7C6395}">
-  <sheetPr/>
+  <sheetPr codeName="Wykres7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8829,7 +8695,7 @@
 
 <file path=xl/chartsheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{93F6BE45-F878-4532-B522-F97639F321B3}">
-  <sheetPr/>
+  <sheetPr codeName="Wykres9"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </chartsheet>
@@ -8839,7 +8705,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -8915,7 +8781,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -8948,7 +8814,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9312088" cy="6084794"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -8981,7 +8847,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9014,7 +8880,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9301370" cy="6071152"/>
+    <xdr:ext cx="9291941" cy="6069654"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Wykres 1">
@@ -9306,6 +9172,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr codeName="Arkusz2"/>
   <dimension ref="A1:AH51"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9563,7 +9430,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EF02CA7-EA61-47C3-B4E3-EF31AF9DB21D}">
-  <sheetPr filterMode="1"/>
+  <sheetPr codeName="Arkusz15" filterMode="1"/>
   <dimension ref="F10:H115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -10703,6 +10570,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{103B2FDA-3C44-468E-A73A-0B88BACC829F}">
+  <sheetPr codeName="Arkusz16"/>
   <dimension ref="F11:H65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -11283,6 +11151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75453D0F-60E5-4E87-9DCE-06B9B6F61869}">
+  <sheetPr codeName="Arkusz4"/>
   <dimension ref="D9:G25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11452,6 +11321,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CE96D4-C4A6-430C-BE52-BF35DE8CF5FB}">
+  <sheetPr codeName="Arkusz6"/>
   <dimension ref="F10:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11742,6 +11612,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ED9AA4D-8C60-46BF-AB6C-23B8DE8D6C04}">
+  <sheetPr codeName="Arkusz8"/>
   <dimension ref="D11:H24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -11944,6 +11815,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35BE90E0-BCD7-47C9-8F6D-B8A505B3EA0F}">
+  <sheetPr codeName="Arkusz10"/>
   <dimension ref="A1:AJ43"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15" zeroHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -12369,6 +12241,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ECAAB5E-582E-4931-90C4-A7B3C0EE8925}">
+  <sheetPr codeName="Arkusz11"/>
   <dimension ref="E8:I17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12503,6 +12376,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BA89615-0346-4103-86DA-934D48E25673}">
+  <sheetPr codeName="Arkusz12"/>
   <dimension ref="E13:S27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12744,6 +12618,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF4E4D0-E921-47DA-9106-99BD60C3C0DF}">
+  <sheetPr codeName="Arkusz13"/>
   <dimension ref="F14:G32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -12887,6 +12762,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38618863-2459-444D-B63B-224360671215}">
+  <sheetPr codeName="Arkusz14"/>
   <dimension ref="F6:J11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
